--- a/pacjenci/ANDRZEJ PIETRAS.xlsx
+++ b/pacjenci/ANDRZEJ PIETRAS.xlsx
@@ -615,10 +615,14 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -662,7 +666,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/pacjenci/ANDRZEJ PIETRAS.xlsx
+++ b/pacjenci/ANDRZEJ PIETRAS.xlsx
@@ -413,279 +413,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>27.07.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Mantle cell lymphoma. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 74mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Aktywne metabolicznie węzły chłonne grup: - 1B po stronie lewej średnicy wg PET 9mm, SUV max 4,7, - 3 po stronie lewej średnicy wg PET 15mm, SUV max 4,6, - 3 po stronie prawej średnicy wg PET 15mm, SUV max 5,5, - 6 po stronie lewej średnicy wg PET 8mm, SUV max 3,2 [lm fuz 73] - 5 po stronie lewej średnicy wg PET do 10mm, SUV max 2,0 [lm fuz 79] - 5 po stronie prawej średnicy wg PET do 10mm, SUV max 1,9 [lm fuz 78] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - pachowe i międzypiersiowe po stronie lewej średnicy wg PET do 14mm, SUV max 5,9 - pachowe i międzypiersiowe po stronie prawej średnicy wg PET do 14mm, SUV max 7,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Tłuszczak w powłokach klatki piersiowej przy mięśniu piersiowym mniejszym i żebrze 4 po stronie lewej 36x20mm.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - przyaortalne po stronie prawej  średnicy wg PET 12mm, SUV max 3,1, [Im fuz 163] - biodrowe zewnętrze i pachwinowe po stronie lewej średnicy wg PET do 15mm, SUV max  do 3,7, - biodrowe zewnętrze i pachwinowe po stronie prawej średnicy wg PET do 18mm, SUV max do 4,9 Niejednorodnie zwiększony metabolizm FDG w znacznie powiększonej śledzionie, w wymiarze dwubiegunowym 244mm, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Prostata powiększona ze zwapnieniami do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z wielopoziomowymi dyskopatiami z objawami próżni.  Wartości referencyjne: MBPS SUVmax 1,2 Prawy płat wątroby SUVmax do 1,9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywną metabolicznie chorobę chłoniakową z zajęciem węzłów chłonnych po obu stronach przepony. Niewykluczone zajęcie śledziony.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>7.3</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>04.11.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Mantle cell lymphoma. Ocena  odpowiedzi po 3 cyklach R-CHOP.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 88mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewelkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.  Pojedyncze drobne węzły chłonne szyjne obustronnie średnicy do 9mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 14mm (SUV max 1,4). Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 41x20mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 146mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe średnicy do 14mm. Prostata wyraźnie powiększona - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.   Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na zastosowane leczenie.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>18.01.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Mantle cell lymphoma. Stan po 6 cyklach R-CHOP. Ocena remisji choroby po zakończeniu ChTh.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 100 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.   Klatka piersiowa i śródpiersie: Wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w segmencie 10 i nieco 9 płuca prawego SUV max do 3,8 - w pierwszej kolejności zmiany zapalne- do kontroli po leczeniu Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 14mm (SUV max 1,4). Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 49x13-20mm.  Brzuch i miednica: Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 157mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe wielkości do 14x5mm. Prostata wyraźnie powiększona - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych, zwłaszcza po stronie prawej SUV max do 4,4- zmiany odczynowo-przeciążeniowe. Wzmożony metabolizm FDG w mięśniach  uda lewego SUV max do 3,9 - zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 3,1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w segmencie 10 i 9 płuca prawego - w pierwszej kolejności zmiany zapalne- do kontroli po leczeniu Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>24.11.2022</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak z komórek strefy płaszcza - wariant klasyczny. Stan po 6 cyklach R-CHOP. Leczenie podtrzymujące rytuksymabem. W badaniu TK powiększenie śledziony, kilka drobnych, niejednoznacznych zmian w miąższu wątroby. Badanie w celu wykluczenia wznowy choroby podstawowej.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 91 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie szyjne węzły chłonne piętra 2, 3, 4 i 5  obustronnie, bardziej liczne po stronie lewej. Największe z nich w piętrze 3 - po stronie prawej o wym. do 17x11x18mm, SUV max do 13,6  [Im fuz 62] oraz po stronie lewej o wym. 14x8x15mm,  SUVmax 8,2  [Im fuz 61] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.   Klatka piersiowa i śródpiersie: Pobudzone, pojedyncze węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 13mm, SUV max 2,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo, w płacie dolnym płuca prawego w segm. 10 zagęszczenia / włóknienia - do oceny klinicznej. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 49x13-20mm.  Brzuch i miednica: Pobudzone metabolicznie węzły chłonne pachwinowe prawe średnicy 8mm, SUVmax do 3,6 [Im fuz 251]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 142mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe wielkości do 14x5mm. Prostata wyraźnie powiększona - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 3,1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy w obrębie węzłów chłonnych szyjnych, pobudzone węzły chłonne pachowe obustronnie oraz pachwinowe prawe. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>13.6</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>05.06.2023</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak z komórek płaszcza dgn 07.2021 na podstawie biopsji szpiku. Stan po 6 cyklach R-CHOP. Leczenie podtrzymujące rytuksymabem - 5 dawka 31.10.2022. Pacjent z powodu progresji choroby otrzymuje lenalidomid w dawce 25 mg 1x dz od 16.02.2023. Stan po zakończeniu 3 cyklu- ostatnia dawka 02.05.23. Ocena odpowiedzi.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 68 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MCL</t>
+          <t>: Bardzo liczne aktywne metabolicznie węzły chłonne szyjne, pojedyncze i spakietowane: - po stronie prawej grup: 1B, 2A, 2B, 3, 4, 5A, 5B, 6 -  wielkości do 17 mm, SUV max do 15,2; - po stronie lewej grup:1B, 2A, 2B, 3, 4, 5A, 5B, 6 oraz przeduszny- wielkości do 24x37 mm, SUV max do 35,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.   Klatka piersiowa i śródpiersie: Liczne aktywne metabolicznie węzły chłonne: - podobojczykowe obustronnie wielkości do 11 mm, SUV max do 11,3; - międzypiersiowe obustronnie wielkości do 22x10 mm, SUV max do 15,5; - pachowe obustronnie  wielkości do 21x18 mm, SUV max do 16,0; - przytchawicze górne i dolne prawe wielkości do 12 mm, SUV max do 32,4; - przytchawicze dolne lewe wielkości do 11x8 mm, SUV max do 13,3; - podostrogowe wielkości do 25x18 mm, SUV max do 26,8; - przyprzełykowe prawe wielkości do 10 mm, SUV max do 11,5 - na poziomie Th7/Th8; - przykręgosłupowe lewe i międzyżebrowe lewe wielkości do 11 mm, SUV max do 8,1; - za prawą kopułą przepony średnicy 7 mm SUV max 5,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate. zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 39x13-23x31mm.  Brzuch i miednica: Bardzo liczne aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - okołoaortalne prawe od poziomu L1/L2 do rozwidlenia aorty, wielkości do 32x15x43 mm, SUV max do 12,9; - okołoaortalne lewe od poziomu L2 do rozwidlenia aorty, wielkości do 16x11 mm, SUV max do 8,5; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych wielkości do 19x44 mm, SUV max do 21,8; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych wielkości do 28x43 mm, SUV max do 11,3; - zasłonowe lewe średnicy  do 10 mm, SUV max do 7,8; - pachwinowe i udowe prawe wielkości do  20x12 mm, SUV max do 14,3; - pachwinowe i udowe lewe wielkości do 30x18 mm, SUV max do 16,6.  Rozlanie wzmożony i niejednorodny metabolizm FDG w powiększonej śledzionie SUV max do 5,4 Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Prostata wyraźnie powiększona - do kontroli urologicznej.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, z nierównym obrysem blaszek granicznych trzonów kręgowych, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z masywnym zajęciem węzłów chłonnych po obu stronach przepony. Niewykluczone zajęcie śledziony. W porównaniu do poprzedniego badania PET/CT z dnia 24.11.2022- znaczna progresja choroby. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>35.3</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5 - znacznie zwiększony wychwyt lub nowe zmiany</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Progresja choroby. Klasyfikacja Lugano: Progressive Disease (PD) - progresja choroby. Deauville: 5 - znacznie zwiększony wychwyt lub nowe zmiany.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ANDRZEJ PIETRAS.xlsx
+++ b/pacjenci/ANDRZEJ PIETRAS.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 74mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne grup: - 1B po stronie lewej średnicy wg PET 9mm, SUV max 4,7, - 3 po stronie lewej średnicy wg PET 15mm, SUV max 4,6, - 3 po stronie prawej średnicy wg PET 15mm, SUV max 5,5, - 6 po stronie lewej średnicy wg PET 8mm, SUV max 3,2 [lm fuz 73] - 5 po stronie lewej średnicy wg PET do 10mm, SUV max 2,0 [lm fuz 79] - 5 po stronie prawej średnicy wg PET do 10mm, SUV max 1,9 [lm fuz 78] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne: - pachowe i międzypiersiowe po stronie lewej średnicy wg PET do 14mm, SUV max 5,9 - pachowe i międzypiersiowe po stronie prawej średnicy wg PET do 14mm, SUV max 7,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Tłuszczak w powłokach klatki piersiowej przy mięśniu piersiowym mniejszym i żebrze 4 po stronie lewej 36x20mm.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - przyaortalne po stronie prawej  średnicy wg PET 12mm, SUV max 3,1, [Im fuz 163] - biodrowe zewnętrze i pachwinowe po stronie lewej średnicy wg PET do 15mm, SUV max  do 3,7, - biodrowe zewnętrze i pachwinowe po stronie prawej średnicy wg PET do 18mm, SUV max do 4,9 Niejednorodnie zwiększony metabolizm FDG w znacznie powiększonej śledzionie, w wymiarze dwubiegunowym 244mm, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Prostata powiększona ze zwapnieniami do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z wielopoziomowymi dyskopatiami z objawami próżni.  Wartości referencyjne: MBPS SUVmax 1,2 Prawy płat wątroby SUVmax do 1,9</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne grup: - 1B po stronie lewej średnicy wg PET 9mm, SUV max 4,7, - 3 po stronie lewej średnicy wg PET 15mm, SUV max 4,6, - 3 po stronie prawej średnicy wg PET 15mm, SUV max 5,5, - 6 po stronie lewej średnicy wg PET 8mm, SUV max 3,2 [lm fuz 73] - 5 po stronie lewej średnicy wg PET do 10mm, SUV max 2,0 [lm fuz 79] - 5 po stronie prawej średnicy wg PET do 10mm, SUV max 1,9 [lm fuz 78] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - pachowe i międzypiersiowe po stronie lewej średnicy wg PET do 14mm, SUV max 5,9 - pachowe i międzypiersiowe po stronie prawej średnicy wg PET do 14mm, SUV max 7,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Tłuszczak w powłokach klatki piersiowej przy mięśniu piersiowym mniejszym i żebrze 4 po stronie lewej 36x20mm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - przyaortalne po stronie prawej  średnicy wg PET 12mm, SUV max 3,1, [Im fuz 163] - biodrowe zewnętrze i pachwinowe po stronie lewej średnicy wg PET do 15mm, SUV max  do 3,7, - biodrowe zewnętrze i pachwinowe po stronie prawej średnicy wg PET do 18mm, SUV max do 4,9 Niejednorodnie zwiększony metabolizm FDG w znacznie powiększonej śledzionie, w wymiarze dwubiegunowym 244mm, SUV max do 5,3. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Prostata powiększona ze zwapnieniami do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z wielopoziomowymi dyskopatiami z objawami próżni.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywną metabolicznie chorobę chłoniakową z zajęciem węzłów chłonnych po obu stronach przepony. Niewykluczone zajęcie śledziony.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>7.3</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 88mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewelkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.  Pojedyncze drobne węzły chłonne szyjne obustronnie średnicy do 9mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 14mm (SUV max 1,4). Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 41x20mm.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 146mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe średnicy do 14mm. Prostata wyraźnie powiększona - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.   Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewelkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.  Pojedyncze drobne węzły chłonne szyjne obustronnie średnicy do 9mm.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 14mm (SUV max 1,4). Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 41x20mm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 146mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe średnicy do 14mm. Prostata wyraźnie powiększona - do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na zastosowane leczenie.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 100 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.   Klatka piersiowa i śródpiersie: Wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w segmencie 10 i nieco 9 płuca prawego SUV max do 3,8 - w pierwszej kolejności zmiany zapalne- do kontroli po leczeniu Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 14mm (SUV max 1,4). Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 49x13-20mm.  Brzuch i miednica: Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 157mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe wielkości do 14x5mm. Prostata wyraźnie powiększona - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych, zwłaszcza po stronie prawej SUV max do 4,4- zmiany odczynowo-przeciążeniowe. Wzmożony metabolizm FDG w mięśniach  uda lewego SUV max do 3,9 - zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 3,1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w segmencie 10 i nieco 9 płuca prawego SUV max do 3,8 - w pierwszej kolejności zmiany zapalne- do kontroli po leczeniu Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 14mm (SUV max 1,4). Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 49x13-20mm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 157mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe wielkości do 14x5mm. Prostata wyraźnie powiększona - do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w mięśniach przykręgosłupowych, zwłaszcza po stronie prawej SUV max do 4,4- zmiany odczynowo-przeciążeniowe. Wzmożony metabolizm FDG w mięśniach  uda lewego SUV max do 3,9 - zmiany odczynowo-przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono wzmożony metabolizm FDG w zmianach naciekowo-włóknistych w segmencie 10 i 9 płuca prawego - w pierwszej kolejności zmiany zapalne- do kontroli po leczeniu Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 91 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie szyjne węzły chłonne piętra 2, 3, 4 i 5  obustronnie, bardziej liczne po stronie lewej. Największe z nich w piętrze 3 - po stronie prawej o wym. do 17x11x18mm, SUV max do 13,6  [Im fuz 62] oraz po stronie lewej o wym. 14x8x15mm,  SUVmax 8,2  [Im fuz 61] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.   Klatka piersiowa i śródpiersie: Pobudzone, pojedyncze węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 13mm, SUV max 2,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo, w płacie dolnym płuca prawego w segm. 10 zagęszczenia / włóknienia - do oceny klinicznej. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 49x13-20mm.  Brzuch i miednica: Pobudzone metabolicznie węzły chłonne pachwinowe prawe średnicy 8mm, SUVmax do 3,6 [Im fuz 251]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 142mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe wielkości do 14x5mm. Prostata wyraźnie powiększona - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 3,1</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie szyjne węzły chłonne piętra 2, 3, 4 i 5  obustronnie, bardziej liczne po stronie lewej. Największe z nich w piętrze 3 - po stronie prawej o wym. do 17x11x18mm, SUV max do 13,6  [Im fuz 62] oraz po stronie lewej o wym. 14x8x15mm,  SUVmax 8,2  [Im fuz 61] Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pobudzone, pojedyncze węzły chłonne pachowe i międzypiersiowe obustronnie średnicy do 13mm, SUV max 2,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste obustronnie nadprzeponowo, w płacie dolnym płuca prawego w segm. 10 zagęszczenia / włóknienia - do oceny klinicznej. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 49x13-20mm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne pachwinowe prawe średnicy 8mm, SUVmax do 3,6 [Im fuz 251]. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Śledziona w wymiarze dwubiegunowym wielkości 142mm.  Nerki o nieco pozaciąganych pozapalnie obrysach. Węzły chłonne okołoaortalne średnicy do 9mm oraz pachwinowe wielkości do 14x5mm. Prostata wyraźnie powiększona - do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy w obrębie węzłów chłonnych szyjnych, pobudzone węzły chłonne pachowe obustronnie oraz pachwinowe prawe. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>13.6</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 68 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Bardzo liczne aktywne metabolicznie węzły chłonne szyjne, pojedyncze i spakietowane: - po stronie prawej grup: 1B, 2A, 2B, 3, 4, 5A, 5B, 6 -  wielkości do 17 mm, SUV max do 15,2; - po stronie lewej grup:1B, 2A, 2B, 3, 4, 5A, 5B, 6 oraz przeduszny- wielkości do 24x37 mm, SUV max do 35,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.   Klatka piersiowa i śródpiersie: Liczne aktywne metabolicznie węzły chłonne: - podobojczykowe obustronnie wielkości do 11 mm, SUV max do 11,3; - międzypiersiowe obustronnie wielkości do 22x10 mm, SUV max do 15,5; - pachowe obustronnie  wielkości do 21x18 mm, SUV max do 16,0; - przytchawicze górne i dolne prawe wielkości do 12 mm, SUV max do 32,4; - przytchawicze dolne lewe wielkości do 11x8 mm, SUV max do 13,3; - podostrogowe wielkości do 25x18 mm, SUV max do 26,8; - przyprzełykowe prawe wielkości do 10 mm, SUV max do 11,5 - na poziomie Th7/Th8; - przykręgosłupowe lewe i międzyżebrowe lewe wielkości do 11 mm, SUV max do 8,1; - za prawą kopułą przepony średnicy 7 mm SUV max 5,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate. zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 39x13-23x31mm.  Brzuch i miednica: Bardzo liczne aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - okołoaortalne prawe od poziomu L1/L2 do rozwidlenia aorty, wielkości do 32x15x43 mm, SUV max do 12,9; - okołoaortalne lewe od poziomu L2 do rozwidlenia aorty, wielkości do 16x11 mm, SUV max do 8,5; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych wielkości do 19x44 mm, SUV max do 21,8; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych wielkości do 28x43 mm, SUV max do 11,3; - zasłonowe lewe średnicy  do 10 mm, SUV max do 7,8; - pachwinowe i udowe prawe wielkości do  20x12 mm, SUV max do 14,3; - pachwinowe i udowe lewe wielkości do 30x18 mm, SUV max do 16,6.  Rozlanie wzmożony i niejednorodny metabolizm FDG w powiększonej śledzionie SUV max do 5,4 Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Prostata wyraźnie powiększona - do kontroli urologicznej.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, z nierównym obrysem blaszek granicznych trzonów kręgowych, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bardzo liczne aktywne metabolicznie węzły chłonne szyjne, pojedyncze i spakietowane: - po stronie prawej grup: 1B, 2A, 2B, 3, 4, 5A, 5B, 6 -  wielkości do 17 mm, SUV max do 15,2; - po stronie lewej grup:1B, 2A, 2B, 3, 4, 5A, 5B, 6 oraz przeduszny- wielkości do 24x37 mm, SUV max do 35,3. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Niewielkie, polipowate zgrubienia błony śluzowej w zachyłkach zębodołowych obu zatok szczękowych.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Liczne aktywne metabolicznie węzły chłonne: - podobojczykowe obustronnie wielkości do 11 mm, SUV max do 11,3; - międzypiersiowe obustronnie wielkości do 22x10 mm, SUV max do 15,5; - pachowe obustronnie  wielkości do 21x18 mm, SUV max do 16,0; - przytchawicze górne i dolne prawe wielkości do 12 mm, SUV max do 32,4; - przytchawicze dolne lewe wielkości do 11x8 mm, SUV max do 13,3; - podostrogowe wielkości do 25x18 mm, SUV max do 26,8; - przyprzełykowe prawe wielkości do 10 mm, SUV max do 11,5 - na poziomie Th7/Th8; - przykręgosłupowe lewe i międzyżebrowe lewe wielkości do 11 mm, SUV max do 8,1; - za prawą kopułą przepony średnicy 7 mm SUV max 5,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie pasmowate. zmiany włókniste obustronnie nadprzeponowo. Tłuszczak w obrębie ściany lewobocznej KLP, w tkance podskórnej głębokiej, w topografii/w przyleganiu do mięśnia piersiowego mniejszego i żebra IV lewego, wielkości ok. 39x13-23x31mm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Bardzo liczne aktywne metabolicznie węzły chłonne pojedyncze i spakietowane: - okołoaortalne prawe od poziomu L1/L2 do rozwidlenia aorty, wielkości do 32x15x43 mm, SUV max do 12,9; - okołoaortalne lewe od poziomu L2 do rozwidlenia aorty, wielkości do 16x11 mm, SUV max do 8,5; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych wielkości do 19x44 mm, SUV max do 21,8; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych wielkości do 28x43 mm, SUV max do 11,3; - zasłonowe lewe średnicy  do 10 mm, SUV max do 7,8; - pachwinowe i udowe prawe wielkości do  20x12 mm, SUV max do 14,3; - pachwinowe i udowe lewe wielkości do 30x18 mm, SUV max do 16,6.  Rozlanie wzmożony i niejednorodny metabolizm FDG w powiększonej śledzionie SUV max do 5,4 Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco pozaciąganych pozapalnie obrysach. Prostata wyraźnie powiększona - do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa, z nierównym obrysem blaszek granicznych trzonów kręgowych, także wielopoziomowo, z objawami próżni krążków międzykręgowych. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z masywnym zajęciem węzłów chłonnych po obu stronach przepony. Niewykluczone zajęcie śledziony. W porównaniu do poprzedniego badania PET/CT z dnia 24.11.2022- znaczna progresja choroby. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>35.3</v>
       </c>
     </row>
